--- a/_FACTORY/_LIGNES/_TEMPLATE/EXPORT/QUIZ_THEME_EXPORT.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/EXPORT/QUIZ_THEME_EXPORT.xlsx
@@ -987,7 +987,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>

--- a/_FACTORY/_LIGNES/_TEMPLATE/EXPORT/QUIZ_THEME_EXPORT.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/EXPORT/QUIZ_THEME_EXPORT.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXPORT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONTROLE_FINAL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLOSSAIRE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,170 +834,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>GLOSSAIRE — ÉTAPE EXPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Source : glossaire_documentaire_factory.md — LECTURE SEULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>TERME</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>DÉFINITION COURTE</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>RÈGLE PRINCIPALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>QA_STATUS</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Résultat final des VALIDATIONS QA_STATUS.</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>[RULE-QA-001] QA_STATUS=FAIL bloque l'export.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>SUFFIXES_ETAT_XLSX</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Indicateurs d'état du fichier tableur tout au long du pipeline.</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[RULE-SUFFIX-001] Tout fichier xlsx doit porter un suffixe d'état.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>STATUS_STANDARD</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Liste officielle des statuts documentaires autorisés.</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>[RULE-STATUS-001] Tout autre format de statut est interdit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>FACTORY_PIPELINE</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Chaîne officielle de traitement documentaire.</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>[RULE-PIPE-001] Aucune étape ne peut être sautée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>NAMING_PATTERN_ARTIFACT</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Fichier pouvant exister en plusieurs exemplaires ou versions dans une même phase.</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>⚠ ALERTES — TERMES POTENTIELLEMENT MANQUANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>L'IA consigne ici tout terme utilisé dans cette étape mais absent du glossaire source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>